--- a/output/doc/functional-module-appendix-20260623-qms-yingtai.xlsx
+++ b/output/doc/functional-module-appendix-20260623-qms-yingtai.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="智能排产" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="璞润" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="瑛泰系统" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续工作" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4363,4 +4364,388 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>一级工作</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>二级工作</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>具体内容</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>主要使用场景</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>补充说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="54" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>展厅模块</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>资料完善</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>持续完善展厅文字资料和图片资料，当前重点是先理顺展示思路和素材框架。</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>展厅内容补强、素材准备</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>目前在图片和文字组织方式上还需要进一步形成统一思路。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="54" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>展厅模块</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>测试与反馈</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>继续开展测试工作，并根据测试过程中的实际反馈进行优化调整。</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>内部测试、体验优化</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>依赖测试侧提供更具体反馈。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="54" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>展厅模块</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>真实图片问题</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>真实图片素材获取和使用仍存在困难，后续需要专题讨论并明确解决方案。</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>素材落地、展示准备</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>属于当前展厅推进中的难点事项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>QMS模块</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>只读功能迭代</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>只读功能已上线，目前由赵海城和王思雨进行测试，后续根据测试结果持续优化。</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>试运行、反馈优化</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>当前已进入测试验证阶段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>QMS模块</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>AI识别适配</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>AI识别产品名称功能已可适用于部分文档，后续继续扩展到更多文档，并安排人工验收。</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>文档识别、人工验收</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>目前适用范围还需要继续扩大。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>QMS模块</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>读取权限前台优化</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>读取权限后台已完成，下一步重点推进前台交互和用户友好性优化。</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>权限使用体验优化</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>重点不在后台能力，而在前台易用性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>QMS模块</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>上传与电子签名</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>在只读、AI识别和读取权限三项工作稳定后，再推进上传功能和电子签名系统建设。</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>功能扩展、合规建设</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>属于后续阶段性新增能力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>eDHR模块</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>内部测试与流程讨论</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>冠骋PPT演示部分已实现约70%，可用于基础内部测试；但整体流程继续推进仍需要更多冠骋经验支持。</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>内部试用、流程完善</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>下一步需要与王博进一步讨论整体流程方案。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>智能排产模块</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>上线测试与迭代</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>计划于本周上线交由赵杰测试，后续根据反馈持续开展迭代优化。</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>试运行、业务适配</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>依赖赵杰测试后的实际使用反馈。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>瑛泰系统</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>傻瓜式运维推进</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>当前已具备基础运维能力，后续继续向傻瓜式运维方向推进，重点实现数据可随时恢复、备份数据不丢失。</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>运维能力提升、稳定性保障</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>重点目标是恢复能力和备份可靠性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>璞润</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>持续迭代优化</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>目前已在算法端和主程序端进行了较深入优化，后续将根据测试结果以及临床提出的需求和问题持续迭代。</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>测试反馈、临床优化</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>重点是稳定性、准确性和临床适用性持续提升。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>